--- a/src/Cinnamon.Web/wwwroot/Template/Masterlist.xlsx
+++ b/src/Cinnamon.Web/wwwroot/Template/Masterlist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rica\source\repos\chockbot\cinnamon\src\Cinnamon.Web\wwwroot\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rica\Source\Repos\chockbot\cinnamon\src\Cinnamon.Web\wwwroot\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1A9AF5-6890-4015-8398-50C832D759B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9289BD-E6F7-4446-A145-018B41E0014B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,9 +38,6 @@
     <t>Enrollee Master List</t>
   </si>
   <si>
-    <t>First Name</t>
-  </si>
-  <si>
     <t>Age</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sessions Attended </t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -494,28 +494,28 @@
     </row>
     <row r="2" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>7</v>
       </c>
       <c r="J2" s="1"/>
     </row>
